--- a/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
+++ b/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-28  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
+          <t>Generated: 2026-07-02  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22).</t>
+          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=1, Familiar Form=2, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=1.88, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="T7" s="12" t="inlineStr">
         <is>
-          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Air 2 Plus has AI chat mode — highest AI tier in Enabot lineup per manufacturer. Product renamed to 'EBO Air 2 Plus FamilyBot'. Review Strength=3: 42 reviews, 5★ (repo data, 2026-06-22).</t>
+          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Air 2 Plus has AI chat mode — highest AI tier in Enabot lineup per manufacturer. Product renamed to 'EBO Air 2 Plus FamilyBot'. Review Strength=3: 42 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>Founded 2022; CES 2025 debut; Series A1 funded (Beijing AI Industry Investment Fund). Privacy=3: local offline AI for daily use; photo uploads encrypted on-device before cloud (ropetai.com). 39°C bionic warmth feature unique in this market (verified Amazon B0GTPZ4N4M). Stationary desktop companion — no locomotion (Movement=1). Brand Reliability=3: legitimate but newer; 30-day returns per manufacturer. Review strength=3: growing — recommend re-check as product matures. Review Strength=2: 17 reviews, 4.3★ (repo data, 2026-06-22).</t>
+          <t>Founded 2022; CES 2025 debut; Series A1 funded (Beijing AI Industry Investment Fund). Privacy=3: local offline AI for daily use; photo uploads encrypted on-device before cloud (ropetai.com). 39°C bionic warmth feature unique in this market (verified Amazon B0GTPZ4N4M). Stationary desktop companion — no locomotion (Movement=1). Brand Reliability=3: legitimate but newer; 30-day returns per manufacturer. Review strength=3: growing — recommend re-check as product matures. Review Strength=2: 17 reviews, 4.3★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=2, Safety=4, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=2.88, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
+++ b/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-02  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
+          <t>Generated: 2026-07-07  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
+++ b/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-07  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
+          <t>Generated: 2026-07-08  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
+++ b/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-08  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
+          <t>Generated: 2026-07-11  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
+++ b/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-11  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
+          <t>Generated: 2026-07-12  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
+++ b/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-12  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
+          <t>Generated: 2026-07-15  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
+++ b/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-15  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
+          <t>Generated: 2026-07-16  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
+++ b/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
@@ -972,7 +972,7 @@
         <v>17</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>4</v>
@@ -984,7 +984,7 @@
         <v>3</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N8" s="9" t="n">
         <v>4</v>

--- a/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
+++ b/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-16  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
+          <t>Generated: 2026-08-10  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
         </is>
       </c>
     </row>
@@ -822,10 +822,10 @@
         <v>499</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>1199</v>
+        <v>1231</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>4.1</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>359</v>
+        <v>319</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>5</v>
@@ -966,10 +966,10 @@
         <v>349</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I8" s="15" t="n">
         <v>3.1</v>

--- a/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
+++ b/Documentation/Best For Lists/Best Premium Robotic Pets List.xlsx
@@ -622,7 +622,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-10  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
+          <t>Generated: 2026-08-13  |  Products shown: 3  |  Eliminated by dedup rule: 2  |  Pre-filter: Price Category equal Premium  (24 products removed)</t>
         </is>
       </c>
     </row>
